--- a/data/credit_bond_all_2026-09-15.xlsx
+++ b/data/credit_bond_all_2026-09-15.xlsx
@@ -721,8 +721,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>70.03</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.90</t>
@@ -8487,7 +8491,7 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -12163,7 +12167,7 @@
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="V52" s="4" t="n">
         <v>3.0</v>
@@ -14892,74 +14896,74 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26宁波通商银行债01</t>
+          <t>26福耀玻璃SCP004</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>09-15 16:30</t>
+          <t>09-15 18:00</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>212680038.IB</t>
+          <t>012682266.IB</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.73Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>25.0</v>
+        <v>6.5</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>25.0</v>
+        <v>6.5</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>38.09</v>
+        <v>22.89</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>25宁波通商银行债02</t>
+          <t>26福耀玻璃SCP003</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2.20Y</t>
+          <t>234D</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.6214</t>
+          <t>1.5474</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>1.6300/1.6200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>宁波通商银行股份有限公司</t>
+          <t>福耀玻璃工业集团股份有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>B- 39.09</t>
+          <t>C+ 32.29</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14969,7 +14973,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>09-15 09:00</t>
+          <t>09-15 10:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -14979,57 +14983,53 @@
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>1.8</v>
+        <v>2.6154</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z64" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将用于优化中长期资产负债匹配结构、增加稳定中长期负债来源并支持中长期资产业务的开展。</t>
+          <t>发行人本次超短期融资券发行金额6.50亿元,用于偿还发行人的金融机构借款</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,国开证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
       <c r="AE64" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF64" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG64" s="3" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>宁波通商银行股份有限公司2026年第一期金融债券</t>
+          <t>福耀玻璃工业集团股份有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15049,60 +15049,60 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t>2027-06-11</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
       <c r="AL64" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr">
+        <is>
+          <t>交运设备制造</t>
+        </is>
+      </c>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>道路运输设备</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>零部件</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>汽车零部件</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM64" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AO64" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ64" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR64" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS64" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT64" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV64" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -15123,27 +15123,29 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AZ64" s="3"/>
+      <c r="AZ64" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26花园CP001</t>
+          <t>26五洲交通MTN001</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-15 18:00</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>042680314.IB</t>
+          <t>102683639.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -15154,29 +15156,33 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>3.60 ~ 4.38</t>
-        </is>
-      </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+          <t>1.60 ~ 2.05</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>48.09</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>25花园CP002</t>
+          <t>25五洲交通MTN002</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>58D</t>
+          <t>2.01Y</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>4.2000</t>
+          <t>1.7874</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -15186,7 +15192,7 @@
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>花园集团有限公司</t>
+          <t>广西五洲交通股份有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -15201,7 +15207,7 @@
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>09-15 09:00</t>
+          <t>09-15 11:00</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -15211,19 +15217,23 @@
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U65" s="4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V65" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>2.94%~2.98%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -15234,28 +15244,28 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券发行规模为2亿元,募集资金拟全部用于偿还公司下属子公司有息负债。</t>
+          <t>本期发行金额2亿元,募集资金拟全部用于偿还发行人及子公司有息负债</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,华夏银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG65" s="3" t="inlineStr">
@@ -15265,7 +15275,7 @@
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>花园集团有限公司2026年度第一期短期融资券</t>
+          <t>广西五洲交通股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
@@ -15275,23 +15285,27 @@
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
-        </is>
-      </c>
-      <c r="AK65" s="3"/>
+          <t>2029-09-16</t>
+        </is>
+      </c>
+      <c r="AK65" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AN65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AO65" s="3" t="inlineStr">
@@ -15301,27 +15315,27 @@
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -15346,131 +15360,143 @@
       </c>
       <c r="AY65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AZ65" s="4" t="n">
-        <v>0.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26法巴银行债02B(BC)</t>
+          <t>26宁波通商银行债01</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>09-15 18:00</t>
+          <t>09-15 16:30</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>292680036.IB</t>
+          <t>212680038.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.05</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>25宁波通商银行债02</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>2.20Y</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>1.6214</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>1.6300/1.6200</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>宁波通商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>B- 39.09</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>09-15 09:00</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U66" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="I66" s="4" t="n">
-        <v>38.35</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>26法巴银行债01B(BC)</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>4.50Y</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>1.8721</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
-          <t>1.8400/--</t>
-        </is>
-      </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>法国巴黎银行</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="inlineStr">
-        <is>
-          <t>B+ 60.00</t>
-        </is>
-      </c>
-      <c r="Q66" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="R66" s="3" t="inlineStr">
-        <is>
-          <t>09-15 09:00</t>
-        </is>
-      </c>
-      <c r="S66" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T66" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="n">
-        <v>2.6</v>
-      </c>
       <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z66" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA66" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>浙江省-宁波市</t>
+        </is>
+      </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本项目下发行债券的募集资金净额可能被转换成其他货币或以人民币形式留存,本期债券发行(即本项目下的第二次发行)的募集资金净额将用于本集团的一般公司用途及业务活动和发展,包括可能以人民币形式为法国巴黎银行(中国)提供流动性支持或用于购买人民币资产等用途。</t>
+          <t>本期债券募集资金将用于优化中长期资产负债匹配结构、增加稳定中长期负债来源并支持中长期资产业务的开展。</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,法国巴黎银行(中国)有限公司,中信建投证券股份有限公司,招商银行股份有限公司,富邦华一银行有限公司,兴业银行股份有限公司,渤海银行股份有限公司,上海浦东发展银行股份有限公司,国泰海通证券股份有限公司,华侨银行有限公司,星展银行(中国)有限公司,中信证券股份有限公司,中国农业银行股份有限公司,三井住友银行(中国)有限公司,中国进出口银行,南京银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
@@ -15481,7 +15507,7 @@
       </c>
       <c r="AF66" s="3" t="inlineStr">
         <is>
-          <t>其他分类</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG66" s="3" t="inlineStr">
@@ -15491,7 +15517,7 @@
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>法国巴黎银行有限公司2026年第二期人民币债券(债券通)(品种二)</t>
+          <t>宁波通商银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -15501,13 +15527,13 @@
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t>2029-09-17</t>
         </is>
       </c>
       <c r="AK66" s="3"/>
       <c r="AL66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AM66" s="3" t="inlineStr">
@@ -15525,7 +15551,11 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP66" s="3"/>
+      <c r="AP66" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -15538,7 +15568,7 @@
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>其他银行</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
@@ -15576,59 +15606,55 @@
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26青岛银行01</t>
+          <t>26花园CP001</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>09-15 16:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>2620008.IB</t>
+          <t>042680314.IB</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>45.0</v>
+        <v>2.0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>45.0</v>
+        <v>2.0</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>34.09</v>
-      </c>
+          <t>3.60 ~ 4.38</t>
+        </is>
+      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>25青岛银行科创债01</t>
+          <t>25花园CP002</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>4.02Y</t>
+          <t>58D</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.6233</t>
+          <t>4.2000</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -15638,12 +15664,12 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>青岛银行股份有限公司</t>
+          <t>花园集团有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>A 71.31</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15666,41 +15692,43 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="U67" s="4" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>2.94%~2.98%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
-        </is>
-      </c>
-      <c r="AB67" s="3"/>
+          <t>浙江省-金华市</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>本期短期融资券发行规模为2亿元,募集资金拟全部用于偿还公司下属子公司有息负债。</t>
+        </is>
+      </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信证券股份有限公司,中银国际证券股份有限公司,申万宏源证券有限公司,华夏银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,恒丰银行股份有限公司,渤海银行股份有限公司</t>
+          <t>浙商银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF67" s="3" t="inlineStr">
@@ -15715,7 +15743,7 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>青岛银行股份有限公司2026年第一期金融债券(债券通)</t>
+          <t>花园集团有限公司2026年度第一期短期融资券</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15725,60 +15753,60 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM67" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AO67" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ67" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR67" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS67" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT67" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU67" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV67" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -15796,15 +15824,17 @@
       </c>
       <c r="AY67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AZ67" s="3"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AZ67" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26五洲交通MTN001</t>
+          <t>26法巴银行债02B(BC)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15814,64 +15844,64 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>102683639.IB</t>
+          <t>292680036.IB</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.05</t>
+          <t>1.65 ~ 2.05</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>48.09</v>
+        <v>38.35</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>25五洲交通MTN002</t>
+          <t>26法巴银行债01B(BC)</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2.01Y</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>1.7874</t>
+          <t>1.8721</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>广西五洲交通股份有限公司</t>
+          <t>法国巴黎银行</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B+ 60.00</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15881,7 +15911,7 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>09-15 11:00</t>
+          <t>09-15 09:00</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -15891,55 +15921,45 @@
       </c>
       <c r="T68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="U68" s="4" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W68" s="3" t="inlineStr">
-        <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X68" s="3" t="inlineStr">
-        <is>
-          <t>1.79%~1.89%</t>
-        </is>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
       <c r="Y68" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z68" s="3"/>
-      <c r="AA68" s="3" t="inlineStr">
-        <is>
-          <t>广西壮族自治区-南宁市</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA68" s="3"/>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元,募集资金拟全部用于偿还发行人及子公司有息负债</t>
+          <t>本项目下发行债券的募集资金净额可能被转换成其他货币或以人民币形式留存,本期债券发行(即本项目下的第二次发行)的募集资金净额将用于本集团的一般公司用途及业务活动和发展,包括可能以人民币形式为法国巴黎银行(中国)提供流动性支持或用于购买人民币资产等用途。</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,法国巴黎银行(中国)有限公司,中信建投证券股份有限公司,招商银行股份有限公司,富邦华一银行有限公司,兴业银行股份有限公司,渤海银行股份有限公司,上海浦东发展银行股份有限公司,国泰海通证券股份有限公司,华侨银行有限公司,星展银行(中国)有限公司,中信证券股份有限公司,中国农业银行股份有限公司,三井住友银行(中国)有限公司,中国进出口银行,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>其他分类</t>
         </is>
       </c>
       <c r="AG68" s="3" t="inlineStr">
@@ -15949,7 +15969,7 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>广西五洲交通股份有限公司2026年度第一期中期票据</t>
+          <t>法国巴黎银行有限公司2026年第二期人民币债券(债券通)(品种二)</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
@@ -15959,57 +15979,49 @@
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
-        </is>
-      </c>
-      <c r="AK68" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-17</t>
+        </is>
+      </c>
+      <c r="AK68" s="3"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AM68" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP68" s="3"/>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他银行</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
@@ -16037,66 +16049,64 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AZ68" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ68" s="3"/>
     </row>
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26冀中能源MTN018B</t>
+          <t>26青岛银行01</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>09-15 18:00</t>
+          <t>09-15 16:00</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>102683649.IB</t>
+          <t>2620008.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>4.0</v>
+        <v>45.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>4.0</v>
+        <v>45.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2.10 ~ 2.70</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>103.09</v>
+        <v>34.09</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>26冀中能源MTN017B</t>
+          <t>25青岛银行科创债01</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+N</t>
+          <t>4.02Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>2.3216</t>
+          <t>1.6233</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -16106,12 +16116,12 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>冀中能源集团有限责任公司</t>
+          <t>青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C 26.79</t>
+          <t>A 71.31</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16121,7 +16131,7 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>09-15 15:00</t>
+          <t>09-15 09:00</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -16131,21 +16141,21 @@
       </c>
       <c r="T69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="U69" s="4" t="n">
-        <v>3.45</v>
+        <v>2.0</v>
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>2.23%~2.33%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -16156,28 +16166,24 @@
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>河北省-邢台市</t>
-        </is>
-      </c>
-      <c r="AB69" s="3" t="inlineStr">
-        <is>
-          <t>本期债务融资工具基础发行金额0亿元，发行金额上限为人民币8亿元。募集资金拟用于偿还发行人的有息债务。</t>
-        </is>
-      </c>
+          <t>山东省-青岛市</t>
+        </is>
+      </c>
+      <c r="AB69" s="3"/>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,东兴证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信证券股份有限公司,中银国际证券股份有限公司,申万宏源证券有限公司,华夏银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,恒丰银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG69" s="3" t="inlineStr">
@@ -16187,7 +16193,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>冀中能源集团有限责任公司2026年度第十八期中期票据(品种二)</t>
+          <t>青岛银行股份有限公司2026年第一期金融债券(债券通)</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -16197,57 +16203,53 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
-        </is>
-      </c>
-      <c r="AK69" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-17</t>
+        </is>
+      </c>
+      <c r="AK69" s="3"/>
       <c r="AL69" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AM69" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
@@ -16262,7 +16264,7 @@
       </c>
       <c r="AW69" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX69" s="3" t="inlineStr">
@@ -16280,7 +16282,7 @@
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26东航SCP004</t>
+          <t>26冀中能源MTN018B</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -16290,64 +16292,64 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>012682269.IB</t>
+          <t>102683649.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>30.0</v>
+        <v>4.0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>30.0</v>
+        <v>4.0</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
+          <t>2.10 ~ 2.70</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1.35</v>
+        <v>2.28</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>14.01</v>
+        <v>103.09</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>26东航SCP003</t>
+          <t>26冀中能源MTN017B</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>205D</t>
+          <t>2.95Y+N</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.5103</t>
+          <t>2.3216</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>--/1.5100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司</t>
+          <t>冀中能源集团有限责任公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>B- 39.34</t>
+          <t>C 26.79</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16357,7 +16359,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>09-15 09:00</t>
+          <t>09-15 15:00</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -16371,19 +16373,17 @@
         </is>
       </c>
       <c r="U70" s="4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.45</v>
+      </c>
+      <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>2.23%~2.33%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -16394,28 +16394,28 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>河北省-邢台市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资发行金额为30亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金。</t>
+          <t>本期债务融资工具基础发行金额0亿元，发行金额上限为人民币8亿元。募集资金拟用于偿还发行人的有息债务。</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司,平安银行股份有限公司</t>
+          <t>兴业证券股份有限公司,东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG70" s="3" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司2026年度第四期超短期融资券</t>
+          <t>冀中能源集团有限责任公司2026年度第十八期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -16435,10 +16435,14 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2027-04-14</t>
-        </is>
-      </c>
-      <c r="AK70" s="3"/>
+          <t>2029-09-16</t>
+        </is>
+      </c>
+      <c r="AK70" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL70" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -16461,27 +16465,27 @@
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16496,7 +16500,7 @@
       </c>
       <c r="AW70" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX70" s="3" t="inlineStr">
@@ -16509,14 +16513,12 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AZ70" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ70" s="3"/>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26凤凰机场MTN002</t>
+          <t>26东航SCP004</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16526,64 +16528,64 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>102683630.IB</t>
+          <t>012682269.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>1.30 ~ 1.51</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>38.35</v>
+        <v>14.01</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>26凤凰机场MTN001</t>
+          <t>26东航SCP003</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2.77Y+2.00Y</t>
+          <t>205D</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.8853</t>
+          <t>1.5103</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5100</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>三亚凤凰国际机场有限责任公司</t>
+          <t>中国东方航空集团有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 39.34</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16607,49 +16609,51 @@
         </is>
       </c>
       <c r="U71" s="4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V71" s="3"/>
+        <v>1.58</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>2.19%~2.29%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>海南省-三亚市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额50,000.00万元,其中46,549.76万元用于提前归还发行人银行贷款、3,450.24万元用于补充流动资金</t>
+          <t>本期超短期融资发行金额为30亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金。</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF71" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG71" s="3" t="inlineStr">
@@ -16659,7 +16663,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>三亚凤凰国际机场有限责任公司2026年度第二期中期票据</t>
+          <t>中国东方航空集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16669,7 +16673,7 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2031-09-16</t>
+          <t>2027-04-14</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
@@ -16695,32 +16699,32 @@
       </c>
       <c r="AP71" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
         <is>
-          <t>2029-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AV71" s="3" t="inlineStr">
@@ -16730,7 +16734,7 @@
       </c>
       <c r="AW71" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX71" s="3" t="inlineStr">
@@ -16750,7 +16754,7 @@
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26福耀玻璃SCP004</t>
+          <t>26凤凰机场MTN002</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -16760,49 +16764,49 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>012682266.IB</t>
+          <t>102683630.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>0.73Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>6.5</v>
+        <v>5.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>6.5</v>
+        <v>5.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22.89</v>
+        <v>38.35</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>26福耀玻璃SCP003</t>
+          <t>26凤凰机场MTN001</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>234D</t>
+          <t>2.77Y+2.00Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.5474</t>
+          <t>1.8853</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -16812,12 +16816,12 @@
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>福耀玻璃工业集团股份有限公司</t>
+          <t>三亚凤凰国际机场有限责任公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.29</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16827,7 +16831,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>09-15 10:00</t>
+          <t>09-15 09:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16841,49 +16845,49 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>2.19%~2.29%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>海南省-三亚市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>发行人本次超短期融资券发行金额6.50亿元,用于偿还发行人的金融机构借款</t>
+          <t>发行人本期发行金额50,000.00万元,其中46,549.76万元用于提前归还发行人银行贷款、3,450.24万元用于补充流动资金</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
       <c r="AE72" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF72" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG72" s="3" t="inlineStr">
@@ -16893,7 +16897,7 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>福耀玻璃工业集团股份有限公司2026年度第四期超短期融资券</t>
+          <t>三亚凤凰国际机场有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -16903,7 +16907,7 @@
       </c>
       <c r="AJ72" s="3" t="inlineStr">
         <is>
-          <t>2027-06-11</t>
+          <t>2031-09-16</t>
         </is>
       </c>
       <c r="AK72" s="3"/>
@@ -16929,32 +16933,32 @@
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
         <is>
-          <t>交运设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>道路运输设备</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>零部件</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AU72" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-16</t>
         </is>
       </c>
       <c r="AV72" s="3" t="inlineStr">
@@ -16964,7 +16968,7 @@
       </c>
       <c r="AW72" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX72" s="3" t="inlineStr">
@@ -17013,8 +17017,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+      <c r="H73" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>44.97</v>
+      </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
           <t>1.86</t>
@@ -17245,8 +17253,12 @@
           <t>2.20 ~ 2.60</t>
         </is>
       </c>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
+      <c r="H74" s="4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>33.25</v>
+      </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
           <t>2.47</t>
@@ -17779,7 +17791,7 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3583</v>
       </c>
       <c r="V76" s="3"/>
       <c r="W76" s="3" t="inlineStr">
@@ -24063,7 +24075,7 @@
         </is>
       </c>
       <c r="U103" s="4" t="n">
-        <v>1.89</v>
+        <v>1.885</v>
       </c>
       <c r="V103" s="4" t="n">
         <v>1.0</v>
